--- a/outputs/analysis/segment_conversion.xlsx
+++ b/outputs/analysis/segment_conversion.xlsx
@@ -7,23 +7,48 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="By Industry" sheetId="1" r:id="rId1"/>
-    <sheet name="By Seniority" sheetId="2" r:id="rId2"/>
+    <sheet name="By Segment" sheetId="1" r:id="rId1"/>
+    <sheet name="By Industry" sheetId="2" r:id="rId2"/>
+    <sheet name="By Seniority" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="48">
+  <si>
+    <t>Segment</t>
+  </si>
+  <si>
+    <t>Deals</t>
+  </si>
+  <si>
+    <t>Won Deals</t>
+  </si>
+  <si>
+    <t>Pipeline ($)</t>
+  </si>
+  <si>
+    <t>Avg Deal ($)</t>
+  </si>
+  <si>
+    <t>Win Rate</t>
+  </si>
+  <si>
+    <t>Commercial</t>
+  </si>
+  <si>
+    <t>Enterprise</t>
+  </si>
+  <si>
+    <t>Mid</t>
+  </si>
   <si>
     <t>Industry</t>
   </si>
   <si>
     <t>Accounts</t>
-  </si>
-  <si>
-    <t>Pipeline ($)</t>
   </si>
   <si>
     <t>Software</t>
@@ -466,10 +491,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -479,225 +504,74 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B2">
-        <v>1865</v>
+        <v>967</v>
       </c>
       <c r="C2">
-        <v>12144117.29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>415</v>
+      </c>
+      <c r="D2">
+        <v>6007564</v>
+      </c>
+      <c r="E2">
+        <v>6219.010351966874</v>
+      </c>
+      <c r="F2">
+        <v>0.4292</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B3">
-        <v>126</v>
+        <v>1583</v>
       </c>
       <c r="C3">
-        <v>2426493</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>487</v>
+      </c>
+      <c r="D3">
+        <v>14642368.02</v>
+      </c>
+      <c r="E3">
+        <v>9267.32153164557</v>
+      </c>
+      <c r="F3">
+        <v>0.3076</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B4">
-        <v>378</v>
+        <v>440</v>
       </c>
       <c r="C4">
-        <v>2386741.9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>486</v>
-      </c>
-      <c r="C5">
-        <v>2306906.6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6">
-        <v>51</v>
-      </c>
-      <c r="C6">
-        <v>719066.75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7">
-        <v>74</v>
-      </c>
-      <c r="C7">
-        <v>457584</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8">
-        <v>59</v>
-      </c>
-      <c r="C8">
-        <v>420729</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9">
-        <v>217</v>
-      </c>
-      <c r="C9">
-        <v>267500</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10">
-        <v>11</v>
-      </c>
-      <c r="C10">
-        <v>177960</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11">
-        <v>15</v>
-      </c>
-      <c r="C11">
-        <v>173842</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12">
-        <v>155</v>
-      </c>
-      <c r="C12">
-        <v>166073</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13">
-        <v>29</v>
-      </c>
-      <c r="C13">
-        <v>162708</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14">
-        <v>9</v>
-      </c>
-      <c r="C14">
-        <v>155190</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15">
-        <v>88</v>
-      </c>
-      <c r="C15">
-        <v>149850</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16">
-        <v>26</v>
-      </c>
-      <c r="C16">
-        <v>136597.5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
-        <v>18</v>
-      </c>
-      <c r="B17">
-        <v>28</v>
-      </c>
-      <c r="C17">
-        <v>112275</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18">
-        <v>32</v>
-      </c>
-      <c r="C18">
-        <v>108268</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>20</v>
-      </c>
-      <c r="B19">
-        <v>79</v>
-      </c>
-      <c r="C19">
-        <v>99838</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20">
-        <v>64</v>
-      </c>
-      <c r="C20">
-        <v>99667</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21">
-        <v>54</v>
-      </c>
-      <c r="C21">
-        <v>96591</v>
+        <v>166</v>
+      </c>
+      <c r="D4">
+        <v>3200348.79</v>
+      </c>
+      <c r="E4">
+        <v>7273.519977272727</v>
+      </c>
+      <c r="F4">
+        <v>0.3773</v>
       </c>
     </row>
   </sheetData>
@@ -707,26 +581,267 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2">
+        <v>1865</v>
+      </c>
+      <c r="C2">
+        <v>12144117.29</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3">
+        <v>126</v>
+      </c>
+      <c r="C3">
+        <v>2426493</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4">
+        <v>378</v>
+      </c>
+      <c r="C4">
+        <v>2386741.9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5">
+        <v>486</v>
+      </c>
+      <c r="C5">
+        <v>2306906.6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6">
+        <v>51</v>
+      </c>
+      <c r="C6">
+        <v>719066.75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7">
+        <v>74</v>
+      </c>
+      <c r="C7">
+        <v>457584</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8">
+        <v>59</v>
+      </c>
+      <c r="C8">
+        <v>420729</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9">
+        <v>217</v>
+      </c>
+      <c r="C9">
+        <v>267500</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10">
+        <v>11</v>
+      </c>
+      <c r="C10">
+        <v>177960</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11">
+        <v>15</v>
+      </c>
+      <c r="C11">
+        <v>173842</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12">
+        <v>155</v>
+      </c>
+      <c r="C12">
+        <v>166073</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13">
+        <v>29</v>
+      </c>
+      <c r="C13">
+        <v>162708</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14">
+        <v>9</v>
+      </c>
+      <c r="C14">
+        <v>155190</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15">
+        <v>88</v>
+      </c>
+      <c r="C15">
+        <v>149850</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16">
+        <v>26</v>
+      </c>
+      <c r="C16">
+        <v>136597.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17">
+        <v>28</v>
+      </c>
+      <c r="C17">
+        <v>112275</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18">
+        <v>32</v>
+      </c>
+      <c r="C18">
+        <v>108268</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19">
+        <v>79</v>
+      </c>
+      <c r="C19">
+        <v>99838</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20">
+        <v>64</v>
+      </c>
+      <c r="C20">
+        <v>99667</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21">
+        <v>54</v>
+      </c>
+      <c r="C21">
+        <v>96591</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="B1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C2">
         <v>62</v>
@@ -734,10 +849,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C3">
         <v>9609</v>
@@ -745,10 +860,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C4">
         <v>190</v>
@@ -756,10 +871,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C5">
         <v>11</v>
@@ -767,10 +882,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C6">
         <v>97</v>
@@ -778,10 +893,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C7">
         <v>8301</v>
@@ -789,10 +904,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C8">
         <v>154</v>
@@ -800,10 +915,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C9">
         <v>53</v>
@@ -811,10 +926,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -822,10 +937,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C11">
         <v>98</v>
@@ -833,10 +948,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C12">
         <v>5103</v>
@@ -844,10 +959,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C13">
         <v>77</v>
@@ -855,10 +970,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C14">
         <v>74</v>
@@ -866,10 +981,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -877,10 +992,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C16">
         <v>5</v>
@@ -888,10 +1003,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C17">
         <v>124</v>
@@ -899,10 +1014,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C18">
         <v>2</v>
@@ -910,10 +1025,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C19">
         <v>2</v>
@@ -921,10 +1036,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C20">
         <v>11</v>
@@ -932,10 +1047,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="B21" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C21">
         <v>1396</v>
@@ -943,10 +1058,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="B22" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C22">
         <v>32</v>
@@ -954,10 +1069,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="B23" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -965,10 +1080,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C24">
         <v>97</v>
@@ -976,10 +1091,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C25">
         <v>3359</v>
@@ -987,10 +1102,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C26">
         <v>11</v>
@@ -998,10 +1113,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C27">
         <v>64</v>
@@ -1009,10 +1124,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C28">
         <v>63</v>
@@ -1020,10 +1135,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="C29">
         <v>32</v>
@@ -1031,10 +1146,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C30">
         <v>36</v>
@@ -1042,10 +1157,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B31" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C31">
         <v>73</v>
@@ -1053,10 +1168,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B32" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C32">
         <v>7449</v>
@@ -1064,10 +1179,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B33" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C33">
         <v>203</v>
@@ -1075,10 +1190,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C34">
         <v>21</v>

--- a/outputs/analysis/segment_conversion.xlsx
+++ b/outputs/analysis/segment_conversion.xlsx
@@ -16,39 +16,42 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="49">
   <si>
     <t>Segment</t>
   </si>
   <si>
-    <t>Deals</t>
+    <t>Resolved Deals</t>
   </si>
   <si>
     <t>Won Deals</t>
   </si>
   <si>
+    <t>Resolved Pipeline ($)</t>
+  </si>
+  <si>
+    <t>Avg Deal ($)</t>
+  </si>
+  <si>
+    <t>Closed-Deal Win Rate</t>
+  </si>
+  <si>
+    <t>Commercial</t>
+  </si>
+  <si>
+    <t>Enterprise</t>
+  </si>
+  <si>
+    <t>Mid</t>
+  </si>
+  <si>
+    <t>Industry</t>
+  </si>
+  <si>
+    <t>Accounts</t>
+  </si>
+  <si>
     <t>Pipeline ($)</t>
-  </si>
-  <si>
-    <t>Avg Deal ($)</t>
-  </si>
-  <si>
-    <t>Win Rate</t>
-  </si>
-  <si>
-    <t>Commercial</t>
-  </si>
-  <si>
-    <t>Enterprise</t>
-  </si>
-  <si>
-    <t>Mid</t>
-  </si>
-  <si>
-    <t>Industry</t>
-  </si>
-  <si>
-    <t>Accounts</t>
   </si>
   <si>
     <t>Software</t>
@@ -519,19 +522,19 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>967</v>
+        <v>888</v>
       </c>
       <c r="C2">
         <v>415</v>
       </c>
       <c r="D2">
-        <v>6007564</v>
+        <v>5107197.5</v>
       </c>
       <c r="E2">
-        <v>6219.010351966874</v>
+        <v>5751.348536036036</v>
       </c>
       <c r="F2">
-        <v>0.4292</v>
+        <v>0.4673</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -539,19 +542,19 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>1583</v>
+        <v>1302</v>
       </c>
       <c r="C3">
         <v>487</v>
       </c>
       <c r="D3">
-        <v>14642368.02</v>
+        <v>9398477.09</v>
       </c>
       <c r="E3">
-        <v>9267.32153164557</v>
+        <v>7218.492388632872</v>
       </c>
       <c r="F3">
-        <v>0.3076</v>
+        <v>0.374</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -559,19 +562,19 @@
         <v>8</v>
       </c>
       <c r="B4">
-        <v>440</v>
+        <v>374</v>
       </c>
       <c r="C4">
         <v>166</v>
       </c>
       <c r="D4">
-        <v>3200348.79</v>
+        <v>2569275.79</v>
       </c>
       <c r="E4">
-        <v>7273.519977272727</v>
+        <v>6869.721363636364</v>
       </c>
       <c r="F4">
-        <v>0.3773</v>
+        <v>0.4439</v>
       </c>
     </row>
   </sheetData>
@@ -592,12 +595,12 @@
         <v>10</v>
       </c>
       <c r="C1" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B2">
         <v>1865</v>
@@ -608,7 +611,7 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3">
         <v>126</v>
@@ -619,7 +622,7 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4">
         <v>378</v>
@@ -630,7 +633,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5">
         <v>486</v>
@@ -641,7 +644,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6">
         <v>51</v>
@@ -652,7 +655,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7">
         <v>74</v>
@@ -663,7 +666,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <v>59</v>
@@ -674,7 +677,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>217</v>
@@ -685,7 +688,7 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10">
         <v>11</v>
@@ -696,7 +699,7 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B11">
         <v>15</v>
@@ -707,7 +710,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12">
         <v>155</v>
@@ -718,7 +721,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13">
         <v>29</v>
@@ -729,7 +732,7 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>9</v>
@@ -740,7 +743,7 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15">
         <v>88</v>
@@ -751,7 +754,7 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16">
         <v>26</v>
@@ -762,7 +765,7 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B17">
         <v>28</v>
@@ -773,7 +776,7 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18">
         <v>32</v>
@@ -784,7 +787,7 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B19">
         <v>79</v>
@@ -795,7 +798,7 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B20">
         <v>64</v>
@@ -806,7 +809,7 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21">
         <v>54</v>
@@ -827,21 +830,21 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C2">
         <v>62</v>
@@ -849,10 +852,10 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C3">
         <v>9609</v>
@@ -860,10 +863,10 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C4">
         <v>190</v>
@@ -871,10 +874,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C5">
         <v>11</v>
@@ -882,10 +885,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C6">
         <v>97</v>
@@ -893,10 +896,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C7">
         <v>8301</v>
@@ -904,10 +907,10 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C8">
         <v>154</v>
@@ -915,10 +918,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9">
         <v>53</v>
@@ -926,10 +929,10 @@
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -937,10 +940,10 @@
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C11">
         <v>98</v>
@@ -948,10 +951,10 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C12">
         <v>5103</v>
@@ -959,10 +962,10 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C13">
         <v>77</v>
@@ -970,10 +973,10 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14">
         <v>74</v>
@@ -981,10 +984,10 @@
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -992,10 +995,10 @@
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C16">
         <v>5</v>
@@ -1003,10 +1006,10 @@
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C17">
         <v>124</v>
@@ -1014,10 +1017,10 @@
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C18">
         <v>2</v>
@@ -1025,10 +1028,10 @@
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C19">
         <v>2</v>
@@ -1036,10 +1039,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C20">
         <v>11</v>
@@ -1047,10 +1050,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C21">
         <v>1396</v>
@@ -1058,10 +1061,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C22">
         <v>32</v>
@@ -1069,10 +1072,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -1080,10 +1083,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C24">
         <v>97</v>
@@ -1091,10 +1094,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B25" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C25">
         <v>3359</v>
@@ -1102,10 +1105,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B26" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C26">
         <v>11</v>
@@ -1113,10 +1116,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B27" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C27">
         <v>64</v>
@@ -1124,10 +1127,10 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C28">
         <v>63</v>
@@ -1135,10 +1138,10 @@
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B29" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C29">
         <v>32</v>
@@ -1146,10 +1149,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C30">
         <v>36</v>
@@ -1157,10 +1160,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B31" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C31">
         <v>73</v>
@@ -1168,10 +1171,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B32" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C32">
         <v>7449</v>
@@ -1179,10 +1182,10 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B33" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C33">
         <v>203</v>
@@ -1190,10 +1193,10 @@
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C34">
         <v>21</v>
